--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3012,6 +3012,67 @@
         <v>7925.28</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>907562-85-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>637</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1180968-36-CM25</t>
+          <t>1233607-44-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3189.63</v>
+        <v>11507.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>908366-100-CM25</t>
+          <t>1233607-43-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>13487.94</v>
+        <v>7602.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057448-562-CM25</t>
+          <t>1180968-36-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>17822.87</v>
+        <v>3189.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1026727-525-CM25</t>
+          <t>908366-100-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9115.280000000001</v>
+        <v>13487.94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>696217-154-CM25</t>
+          <t>1057448-562-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10754.74</v>
+        <v>17822.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2013-2460-CM25</t>
+          <t>1026727-525-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,43 +874,43 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>39727.85</v>
+        <v>9115.280000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>628-503-CM25</t>
+          <t>696217-154-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10594.52</v>
+        <v>10754.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1026727-572-CM25</t>
+          <t>2013-2460-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11752.87</v>
+        <v>39727.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1026727-570-CM25</t>
+          <t>628-503-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4630.93</v>
+        <v>10594.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2013-2578-CM25</t>
+          <t>1026727-572-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>76.011.397-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2464.23</v>
+        <v>11752.87</v>
       </c>
     </row>
     <row r="12">
@@ -1185,7 +1185,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1053139-4-CM26</t>
+          <t>2013-2578-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3936.42</v>
+        <v>2464.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>907562-2-CM26</t>
+          <t>1026727-570-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11021.26</v>
+        <v>4630.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3885-42-CM26</t>
+          <t>1053139-4-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>16834.5</v>
+        <v>3936.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3885-43-CM26</t>
+          <t>907562-2-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>13290.4</v>
+        <v>11021.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2013-176-CM26</t>
+          <t>3885-42-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6806.8</v>
+        <v>16834.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2013-187-CM26</t>
+          <t>3885-43-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3070.2</v>
+        <v>13290.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3447-450-CM26</t>
+          <t>2013-176-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17612</v>
+        <v>6806.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2013-223-CM26</t>
+          <t>2013-187-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>74380.95</v>
+        <v>3070.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2404-218-CM26</t>
+          <t>3447-450-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>32034.5</v>
+        <v>17612</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2404-209-CM26</t>
+          <t>2013-223-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4389.09</v>
+        <v>74380.95</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3447-732-CM26</t>
+          <t>2404-218-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2562.83</v>
+        <v>32034.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2013-516-CM26</t>
+          <t>2404-209-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6640.2</v>
+        <v>4389.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2013-536-CM26</t>
+          <t>3447-732-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8139.6</v>
+        <v>2562.83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2013-539-CM26</t>
+          <t>2013-516-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>44724.1</v>
+        <v>6640.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2013-604-CM26</t>
+          <t>2013-536-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>27268.56</v>
+        <v>8139.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3447-1139-CM26</t>
+          <t>2013-539-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>867.51</v>
+        <v>44724.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2013-787-CM26</t>
+          <t>2013-604-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3854.89</v>
+        <v>27268.56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1077499-51-CM26</t>
+          <t>3447-1139-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>522.4</v>
+        <v>867.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2591-421-CM26</t>
+          <t>2013-787-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15080.6</v>
+        <v>3854.89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>768-200-CM26</t>
+          <t>1077499-51-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>72.223.100-7</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>11889.74</v>
+        <v>522.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>768-199-CM26</t>
+          <t>2591-421-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>72.223.100-7</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2060.6</v>
+        <v>15080.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2013-933-CM26</t>
+          <t>768-200-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2289.54</v>
+        <v>11889.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2013-1041-CM26</t>
+          <t>768-199-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>8969.91</v>
+        <v>2060.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2013-1044-CM26</t>
+          <t>2013-933-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1862.02</v>
+        <v>2289.54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1077499-56-CM26</t>
+          <t>2013-1041-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>14626.34</v>
+        <v>8969.91</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3159-108-CM26</t>
+          <t>2013-1044-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5490.07</v>
+        <v>1862.02</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3447-1876-CM26</t>
+          <t>1077499-56-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>8923.959999999999</v>
+        <v>14626.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1053139-91-CM26</t>
+          <t>3159-108-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,22 +2847,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>963.9</v>
+        <v>5490.07</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1233607-63-CM26</t>
+          <t>3447-1876-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>17846.64</v>
+        <v>8923.959999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1501513-90-CM26</t>
+          <t>1053139-91-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública del Tamarugal</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7925.28</v>
+        <v>963.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>907562-85-CM26</t>
+          <t>1233607-63-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,6 +3070,128 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
+        <v>17846.64</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1501513-90-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.981.030-9</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública del Tamarugal</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>7925.28</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>907562-85-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
         <v>637</v>
       </c>
     </row>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1233607-44-CM25</t>
+          <t>3447-23-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11507.3</v>
+        <v>2402.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1233607-43-CM25</t>
+          <t>3447-28-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7602.43</v>
+        <v>6913.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1180968-36-CM25</t>
+          <t>1026727-25-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3189.63</v>
+        <v>30080.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>908366-100-CM25</t>
+          <t>3447-571-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13487.94</v>
+        <v>4267.21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057448-562-CM25</t>
+          <t>908366-8-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>17822.87</v>
+        <v>10930.86</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1026727-525-CM25</t>
+          <t>2404-160-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9115.280000000001</v>
+        <v>34614.79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>696217-154-CM25</t>
+          <t>1305552-26-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,43 +935,43 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10754.74</v>
+        <v>4126.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2013-2460-CM25</t>
+          <t>1305552-41-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,28 +996,28 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>39727.85</v>
+        <v>13727.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>628-503-CM25</t>
+          <t>768-163-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,43 +1057,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10594.52</v>
+        <v>16111.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1026727-572-CM25</t>
+          <t>1426397-90-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,43 +1118,43 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>11752.87</v>
+        <v>10248.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2013-2579-CM25</t>
+          <t>1426397-105-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3124.52</v>
+        <v>4950.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2013-2578-CM25</t>
+          <t>3447-1324-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,43 +1240,43 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2464.23</v>
+        <v>3133.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1026727-570-CM25</t>
+          <t>2013-690-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,43 +1301,43 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4630.93</v>
+        <v>32229.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1053139-4-CM26</t>
+          <t>1058339-224-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,28 +1362,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3936.42</v>
+        <v>13119.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>907562-2-CM26</t>
+          <t>1233607-43-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,28 +1423,28 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>11021.26</v>
+        <v>7602.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3885-42-CM26</t>
+          <t>1233607-44-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,28 +1484,28 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>16834.5</v>
+        <v>11507.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3885-43-CM26</t>
+          <t>1058339-234-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>69.010.200-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE HUARA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,43 +1545,43 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13290.4</v>
+        <v>9509.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2013-176-CM26</t>
+          <t>1077499-77-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,43 +1606,43 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6806.8</v>
+        <v>11868.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2013-187-CM26</t>
+          <t>1417913-157-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,28 +1667,28 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3070.2</v>
+        <v>7565.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3447-450-CM26</t>
+          <t>3352-203-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,43 +1728,43 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>17612</v>
+        <v>3534.24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2013-223-CM26</t>
+          <t>768-426-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,43 +1789,43 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>74380.95</v>
+        <v>4495.52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2404-218-CM26</t>
+          <t>3447-2625-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,28 +1850,28 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>32034.5</v>
+        <v>12297.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2404-209-CM26</t>
+          <t>951-1829-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,43 +1911,43 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4389.09</v>
+        <v>7754.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3447-732-CM26</t>
+          <t>2404-909-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,43 +1972,43 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2562.83</v>
+        <v>42611.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2013-516-CM26</t>
+          <t>768-481-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,43 +2033,43 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6640.2</v>
+        <v>2243.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2013-536-CM26</t>
+          <t>1476917-2-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,28 +2094,28 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8139.6</v>
+        <v>45337.81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2013-539-CM26</t>
+          <t>1417913-171-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,28 +2155,28 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>44724.1</v>
+        <v>3617.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2013-604-CM26</t>
+          <t>1417913-305-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,43 +2216,43 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>27268.56</v>
+        <v>8945.129999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3447-1139-CM26</t>
+          <t>2013-1584-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,28 +2277,28 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>867.51</v>
+        <v>34461.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2013-787-CM26</t>
+          <t>2013-1583-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,43 +2338,43 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3854.89</v>
+        <v>8615.360000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1077499-51-CM26</t>
+          <t>1417913-376-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,43 +2399,43 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>522.4</v>
+        <v>12723.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2591-421-CM26</t>
+          <t>4029-160-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,28 +2460,28 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>15080.6</v>
+        <v>23340.66</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>768-200-CM26</t>
+          <t>575924-127-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>72.223.100-7</t>
+          <t>60.318.000-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,43 +2521,43 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>11889.74</v>
+        <v>7276.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>768-199-CM26</t>
+          <t>1180968-36-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>72.223.100-7</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,43 +2582,43 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2060.6</v>
+        <v>3189.63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2013-933-CM26</t>
+          <t>908366-100-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,43 +2643,43 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2289.54</v>
+        <v>13487.94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2013-1041-CM26</t>
+          <t>1057448-562-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,43 +2704,43 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>8969.91</v>
+        <v>17822.87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2013-1044-CM26</t>
+          <t>1026727-525-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,43 +2765,43 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1862.02</v>
+        <v>9115.280000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1077499-56-CM26</t>
+          <t>696217-154-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>14626.34</v>
+        <v>10754.74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3159-108-CM26</t>
+          <t>2013-2460-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5490.07</v>
+        <v>39727.85</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3447-1876-CM26</t>
+          <t>628-503-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8923.959999999999</v>
+        <v>10594.52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1053139-91-CM26</t>
+          <t>1026727-570-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,27 +2964,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>963.9</v>
+        <v>4630.93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1233607-63-CM26</t>
+          <t>2013-2578-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>17846.64</v>
+        <v>2464.23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1501513-90-CM26</t>
+          <t>2013-2579-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,27 +3086,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública del Tamarugal</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7925.28</v>
+        <v>3124.52</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>907562-85-CM26</t>
+          <t>1026727-572-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.011.397-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,7 +3192,2020 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
+        <v>11752.87</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1053139-4-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>3936.42</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>907562-2-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>11021.26</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3885-42-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>16834.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3885-43-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>13290.4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2013-176-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>6806.8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2013-187-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>3070.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3447-450-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>17612</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2013-223-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>74380.95</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2404-209-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>4389.09</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2404-218-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>COMPUNOW SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>78.218.816-K</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>32034.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3447-732-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>2562.83</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2013-516-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>6640.2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2013-536-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>8139.6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2013-539-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>44724.1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2013-604-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>27268.56</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3447-1139-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Clevertec</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>867.51</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2013-787-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>3854.89</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1077499-51-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>61.606.100-3</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>522.4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2591-421-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>83.017.500-8</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>15080.6</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>768-200-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>72.223.100-7</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>11889.74</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>768-199-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>72.223.100-7</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>2060.6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2013-933-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>SANDOS SPA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>2289.54</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2013-1041-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>8969.91</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2013-1044-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>77.727.285-3</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>1862.02</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1077499-56-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.606.100-3</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>14626.34</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3159-108-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.102.038-4</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>5490.07</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3447-1876-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>8923.959999999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1053139-91-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>963.9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1233607-63-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>61.980.910-6</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Iquique</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>17846.64</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1501513-90-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.981.030-9</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública del Tamarugal</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>7925.28</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>3447-2326-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>1694.56</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>907562-85-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
         <v>637</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1055513-2-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>60.511.010-K</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>2545.77</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1233607-43-CM25</t>
+          <t>1233607-44-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7602.43</v>
+        <v>11507.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1233607-44-CM25</t>
+          <t>1233607-43-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11507.3</v>
+        <v>7602.43</v>
       </c>
     </row>
     <row r="18">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2832,7 +2832,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2013-2460-CM25</t>
+          <t>1422259-63-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.042.904-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>39727.85</v>
+        <v>6830.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>628-503-CM25</t>
+          <t>2013-2460-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>10594.52</v>
+        <v>39727.85</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1026727-570-CM25</t>
+          <t>1026727-572-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>76.011.397-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4630.93</v>
+        <v>11752.87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2013-2578-CM25</t>
+          <t>1026727-570-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2464.23</v>
+        <v>4630.93</v>
       </c>
     </row>
     <row r="44">
@@ -3137,7 +3137,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1026727-572-CM25</t>
+          <t>2013-2578-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>11752.87</v>
+        <v>2464.23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1053139-4-CM26</t>
+          <t>1417913-12-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3936.42</v>
+        <v>8005.57</v>
       </c>
     </row>
     <row r="47">
@@ -3564,7 +3564,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3447-450-CM26</t>
+          <t>1417913-174-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>17612</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2013-223-CM26</t>
+          <t>3447-450-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,22 +3640,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>74380.95</v>
+        <v>17612</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2404-209-CM26</t>
+          <t>2013-223-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4389.09</v>
+        <v>74380.95</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2404-218-CM26</t>
+          <t>1305552-28-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>32034.5</v>
+        <v>12944.57</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3447-732-CM26</t>
+          <t>2404-218-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2562.83</v>
+        <v>32034.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2013-516-CM26</t>
+          <t>2404-209-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6640.2</v>
+        <v>4389.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2013-536-CM26</t>
+          <t>3447-732-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,27 +3940,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8139.6</v>
+        <v>2562.83</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2013-539-CM26</t>
+          <t>2013-516-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>44724.1</v>
+        <v>6640.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2013-604-CM26</t>
+          <t>2013-536-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>27268.56</v>
+        <v>8139.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3447-1139-CM26</t>
+          <t>2013-539-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,22 +4128,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>867.51</v>
+        <v>44724.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2013-787-CM26</t>
+          <t>2013-604-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3854.89</v>
+        <v>27268.56</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1077499-51-CM26</t>
+          <t>3447-1139-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>522.4</v>
+        <v>867.51</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2591-421-CM26</t>
+          <t>1417913-324-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>15080.6</v>
+        <v>4719.33</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>768-200-CM26</t>
+          <t>2013-787-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,27 +4367,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>72.223.100-7</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>11889.74</v>
+        <v>3854.89</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>768-199-CM26</t>
+          <t>1077499-51-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>72.223.100-7</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2060.6</v>
+        <v>522.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2013-933-CM26</t>
+          <t>2591-421-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2289.54</v>
+        <v>15080.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2013-1041-CM26</t>
+          <t>768-199-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,22 +4555,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>8969.91</v>
+        <v>2060.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2013-1044-CM26</t>
+          <t>768-200-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,22 +4616,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1862.02</v>
+        <v>11889.74</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1077499-56-CM26</t>
+          <t>2013-933-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,22 +4677,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>14626.34</v>
+        <v>2289.54</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3159-108-CM26</t>
+          <t>2013-1041-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,27 +4733,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5490.07</v>
+        <v>8969.91</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3447-1876-CM26</t>
+          <t>2013-1044-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,27 +4794,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>8923.959999999999</v>
+        <v>1862.02</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1053139-91-CM26</t>
+          <t>1077499-56-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,27 +4855,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>963.9</v>
+        <v>14626.34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1233607-63-CM26</t>
+          <t>3159-108-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,22 +4921,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>17846.64</v>
+        <v>5490.07</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1501513-90-CM26</t>
+          <t>3447-1876-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública del Tamarugal</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7925.28</v>
+        <v>8923.959999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3447-2326-CM26</t>
+          <t>1233607-63-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1694.56</v>
+        <v>17846.64</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>907562-85-CM26</t>
+          <t>1501513-90-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>637</v>
+        <v>7925.28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1055513-2-CM26</t>
+          <t>1305552-92-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,7 +5205,556 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
+        <v>1053.15</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>3447-2326-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>1694.56</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>907562-85-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.010.400-8</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PICA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1055513-2-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>60.511.010-K</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
         <v>2545.77</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>768-312-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>72.223.100-7</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>AURA XD SPA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.359.312-6</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>4496.18</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>951-48-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>60.511.010-K</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2013-1417-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>I.I.A. Ltda.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>5562-31-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>61.979.010-3</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>3226.89</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1426394-112-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>61.980.910-6</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Iquique</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>I.I.A. Ltda.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>43363.6</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1426397-244-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>61.980.910-6</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Iquique</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>I.I.A. Ltda.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>31438.61</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
@@ -562,7 +562,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1643,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1708,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1834,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1960,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2025,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2090,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2155,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2220,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2285,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2350,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2415,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2480,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2545,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2610,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2675,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2740,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2805,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2870,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2935,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3000,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3065,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3191,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3256,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3382,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3447,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3512,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3577,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3764,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3829,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3894,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3959,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4024,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4089,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4154,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4219,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4406,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4593,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4658,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4784,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4910,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4975,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5040,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5105,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5170,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5235,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5300,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5365,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5491,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5556,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5621,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5747,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1851,7 +1851,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3447-2625-CM25</t>
+          <t>951-1829-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1891,28 +1891,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>12297.41</v>
+        <v>7754.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>951-1829-CM25</t>
+          <t>3447-2625-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1932,17 +1936,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1952,26 +1956,22 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7754.12</v>
+        <v>12297.41</v>
       </c>
     </row>
     <row r="25">
@@ -3594,7 +3594,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2013-176-CM26</t>
+          <t>2013-187-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3649,13 +3649,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>6806.8</v>
+        <v>3070.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2013-187-CM26</t>
+          <t>2013-176-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3070.2</v>
+        <v>6806.8</v>
       </c>
     </row>
     <row r="52">
@@ -5317,7 +5317,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1501513-90-CM26</t>
+          <t>1305552-92-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5357,32 +5357,28 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7925.28</v>
+        <v>1053.15</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1305552-92-CM26</t>
+          <t>1501513-90-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5402,7 +5398,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5422,22 +5418,26 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1053.15</v>
+        <v>7925.28</v>
       </c>
     </row>
     <row r="79">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5886,7 +5886,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1426394-112-CM26</t>
+          <t>1426397-244-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>43363.6</v>
+        <v>31438.61</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1426397-244-CM26</t>
+          <t>1426394-112-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6002,7 +6002,259 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>31438.61</v>
+        <v>43363.6</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>3413-84-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>61.971.700-7</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>3725.51</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>3447-2829-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>1344.7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2013-1634-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>4303.04</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2013-1633-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>34136.27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/tarapaca.xlsx
@@ -5337,7 +5337,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
